--- a/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
@@ -1621,7 +1621,7 @@
       <formula1>"Quincenal,Mensual,Semanal,Decenal"</formula1>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B7">
-      <formula1>"Resto del país,Zona Libre de la Frontera Norte"</formula1>
+      <formula1>'Tablas oficiales'!$B$4:$B$5</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Escribe un número entre 0 y 60." sqref="B8">
       <formula1>0</formula1>
@@ -1930,7 +1930,7 @@
       <formula2>1000000000000</formula2>
     </dataValidation>
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B9">
-      <formula1>"Resto del país,Zona Libre de la Frontera Norte"</formula1>
+      <formula1>'Tablas oficiales'!$B$4:$B$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2422,7 +2422,7 @@
   </mergeCells>
   <dataValidations count="11">
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B10">
-      <formula1>"Resto del país,Zona Libre de la Frontera Norte"</formula1>
+      <formula1>'Tablas oficiales'!$B$4:$B$5</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Escribe un número entre 0 y 31." sqref="B11">
       <formula1>0</formula1>

--- a/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito y liquidación»: pones tus fechas y tu sueldo, y te dice el finiquito (salarios, aguinaldo, vacaciones y primas) y, si te despidieron sin causa justificada, la liquidación.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 8/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -407,7 +407,7 @@
     <t>Tablas oficiales de México</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 8/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2032,7 +2032,7 @@
         <v>87</v>
       </c>
       <c r="B9" s="26">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>88</v>

--- a/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito y liquidación»: pones tus fechas y tu sueldo, y te dice el finiquito (salarios, aguinaldo, vacaciones y primas) y, si te despidieron sin causa justificada, la liquidación.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 12/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -407,7 +407,7 @@
     <t>Tablas oficiales de México</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 12/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2032,7 +2032,7 @@
         <v>87</v>
       </c>
       <c r="B9" s="26">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>88</v>

--- a/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito y liquidación»: pones tus fechas y tu sueldo, y te dice el finiquito (salarios, aguinaldo, vacaciones y primas) y, si te despidieron sin causa justificada, la liquidación.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 12/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 13/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -407,7 +407,7 @@
     <t>Tablas oficiales de México</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 12/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 13/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2032,7 +2032,7 @@
         <v>87</v>
       </c>
       <c r="B9" s="26">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>88</v>

--- a/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito y liquidación»: pones tus fechas y tu sueldo, y te dice el finiquito (salarios, aguinaldo, vacaciones y primas) y, si te despidieron sin causa justificada, la liquidación.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -407,7 +407,7 @@
     <t>Tablas oficiales de México</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2032,7 +2032,7 @@
         <v>87</v>
       </c>
       <c r="B9" s="26">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>88</v>

--- a/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito y liquidación»: pones tus fechas y tu sueldo, y te dice el finiquito (salarios, aguinaldo, vacaciones y primas) y, si te despidieron sin causa justificada, la liquidación.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -407,7 +407,7 @@
     <t>Tablas oficiales de México</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2032,7 +2032,7 @@
         <v>87</v>
       </c>
       <c r="B9" s="26">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>88</v>

--- a/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito y liquidación»: pones tus fechas y tu sueldo, y te dice el finiquito (salarios, aguinaldo, vacaciones y primas) y, si te despidieron sin causa justificada, la liquidación.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -407,7 +407,7 @@
     <t>Tablas oficiales de México</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2032,7 +2032,7 @@
         <v>87</v>
       </c>
       <c r="B9" s="26">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>88</v>

--- a/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito y liquidación»: pones tus fechas y tu sueldo, y te dice el finiquito (salarios, aguinaldo, vacaciones y primas) y, si te despidieron sin causa justificada, la liquidación.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -407,7 +407,7 @@
     <t>Tablas oficiales de México</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2032,7 +2032,7 @@
         <v>87</v>
       </c>
       <c r="B9" s="26">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>88</v>

--- a/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="195">
   <si>
     <t>Planilla de sueldo y finiquito México 2026</t>
   </si>
@@ -32,7 +32,7 @@
     <t>«Finiquito y liquidación»: pones tus fechas y tu sueldo, y te dice el finiquito (salarios, aguinaldo, vacaciones y primas) y, si te despidieron sin causa justificada, la liquidación.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -50,6 +50,12 @@
     <t>Sueldo neto: ISR, subsidio y cuotas del IMSS</t>
   </si>
   <si>
+    <t>Resto del país</t>
+  </si>
+  <si>
+    <t>Zona Libre de la Frontera Norte</t>
+  </si>
+  <si>
     <t>Paso a paso</t>
   </si>
   <si>
@@ -74,9 +80,6 @@
     <t>Dónde trabajas</t>
   </si>
   <si>
-    <t>Resto del país</t>
-  </si>
-  <si>
     <t>Divisor del salario diario (LFT art. 89)</t>
   </si>
   <si>
@@ -407,7 +410,7 @@
     <t>Tablas oficiales de México</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -444,9 +447,6 @@
   </si>
   <si>
     <t>7/10/2026</t>
-  </si>
-  <si>
-    <t>Zona Libre de la Frontera Norte</t>
   </si>
   <si>
     <t>Tarifa de retención del ISR para pagos de 7 días</t>
@@ -1318,7 +1318,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1327,48 +1327,57 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
+      <c r="Z1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" s="8">
         <v>10000</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="12">
         <f>IF(B6="Mensual",30.4,IF(B6="Quincenal",15,IF(B6="Semanal",7,10)))</f>
@@ -1376,13 +1385,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="12">
         <f>IF(B6="Mensual",30,F6)</f>
@@ -1390,16 +1399,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="13">
         <v>1</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="15">
         <f>ROUND(B5/F7,2)</f>
@@ -1407,14 +1416,14 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="15">
         <f>INDEX('Tablas oficiales'!$C$4:$C$5,MATCH(B7,'Tablas oficiales'!$B$4:$B$5,0))</f>
@@ -1422,7 +1431,7 @@
     </row>
     <row r="10" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E10" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" s="16">
         <f>IF(F8&lt;=F9,"Sí","No")</f>
@@ -1430,31 +1439,31 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="18">
         <f>F8</f>
       </c>
       <c r="E12" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" s="18">
         <f>ROUND(F24,2)</f>
       </c>
       <c r="E13" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13" s="15">
         <f>IF(F10="Sí",0,ROUND(IF(B6="Semanal",IF(B5&lt;=0,0,INDEX('Tablas oficiales'!$E$8:$E$18,IFERROR(MATCH(B5,'Tablas oficiales'!$B$8:$B$18,1),1))+(B5-INDEX('Tablas oficiales'!$B$8:$B$18,IFERROR(MATCH(B5,'Tablas oficiales'!$B$8:$B$18,1),1)))*INDEX('Tablas oficiales'!$D$8:$D$18,IFERROR(MATCH(B5,'Tablas oficiales'!$B$8:$B$18,1),1))/100),IF(B6="Decenal",IF(B5&lt;=0,0,INDEX('Tablas oficiales'!$E$22:$E$32,IFERROR(MATCH(B5,'Tablas oficiales'!$B$22:$B$32,1),1))+(B5-INDEX('Tablas oficiales'!$B$22:$B$32,IFERROR(MATCH(B5,'Tablas oficiales'!$B$22:$B$32,1),1)))*INDEX('Tablas oficiales'!$D$22:$D$32,IFERROR(MATCH(B5,'Tablas oficiales'!$B$22:$B$32,1),1))/100),IF(B6="Quincenal",IF(B5&lt;=0,0,INDEX('Tablas oficiales'!$E$36:$E$46,IFERROR(MATCH(B5,'Tablas oficiales'!$B$36:$B$46,1),1))+(B5-INDEX('Tablas oficiales'!$B$36:$B$46,IFERROR(MATCH(B5,'Tablas oficiales'!$B$36:$B$46,1),1)))*INDEX('Tablas oficiales'!$D$36:$D$46,IFERROR(MATCH(B5,'Tablas oficiales'!$B$36:$B$46,1),1))/100),IF(B5&lt;=0,0,INDEX('Tablas oficiales'!$E$50:$E$60,IFERROR(MATCH(B5,'Tablas oficiales'!$B$50:$B$60,1),1))+(B5-INDEX('Tablas oficiales'!$B$50:$B$60,IFERROR(MATCH(B5,'Tablas oficiales'!$B$50:$B$60,1),1)))*INDEX('Tablas oficiales'!$D$50:$D$60,IFERROR(MATCH(B5,'Tablas oficiales'!$B$50:$B$60,1),1))/100)))),2))</f>
@@ -1462,13 +1471,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="18">
         <f>F13</f>
       </c>
       <c r="E14" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F14" s="15">
         <f>'Tablas oficiales'!$C$62*'Tablas oficiales'!$C$63/100</f>
@@ -1476,13 +1485,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="18">
         <f>F17</f>
       </c>
       <c r="E15" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F15" s="15">
         <f>IF(B6="Mensual",F14,F14/30.4*F6)</f>
@@ -1490,13 +1499,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="18">
         <f>F18</f>
       </c>
       <c r="E16" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F16" s="15">
         <f>IF(B6="Mensual",B5,B5/F6*30.4)</f>
@@ -1504,13 +1513,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="18">
         <f>F28</f>
       </c>
       <c r="E17" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F17" s="15">
         <f>IF(F10="Sí",0,IF(F16&lt;='Tablas oficiales'!$C$64,MIN(ROUND(F15,2),F13),0))</f>
@@ -1518,13 +1527,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="20">
         <f>ROUND(B5-F18-F28,2)</f>
       </c>
       <c r="E18" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F18" s="15">
         <f>ROUND(F13-F17,2)</f>
@@ -1532,17 +1541,17 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="E20" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E21" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F21" s="21">
         <f>IF(MAX(1,B8)&lt;1,0,IF(MAX(1,B8)&lt;=5,'Tablas oficiales'!$C$65+2*(MAX(1,B8)-1),'Tablas oficiales'!$C$65+8+2*ROUNDUP((MAX(1,B8)-5)/5,0)))</f>
@@ -1550,7 +1559,7 @@
     </row>
     <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E22" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F22" s="22">
         <f>1+('Tablas oficiales'!$C$66+F21*'Tablas oficiales'!$C$67/100)/365</f>
@@ -1558,7 +1567,7 @@
     </row>
     <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E23" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F23" s="15">
         <f>IF(ISNUMBER(B9),B9,ROUND(F8*F22,2))</f>
@@ -1566,7 +1575,7 @@
     </row>
     <row r="24" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E24" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F24" s="15">
         <f>MIN(MAX(F23,F9),'Tablas oficiales'!$C$69*'Tablas oficiales'!$C$68)</f>
@@ -1574,7 +1583,7 @@
     </row>
     <row r="25" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E25" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F25" s="23">
         <f>'Tablas oficiales'!$C$71+'Tablas oficiales'!$C$72+'Tablas oficiales'!$C$73+'Tablas oficiales'!$C$74</f>
@@ -1582,7 +1591,7 @@
     </row>
     <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E26" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F26" s="15">
         <f>MAX(0,F24-'Tablas oficiales'!$C$75*'Tablas oficiales'!$C$68)</f>
@@ -1590,7 +1599,7 @@
     </row>
     <row r="27" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E27" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F27" s="12">
         <f>F24*F25/100+F26*'Tablas oficiales'!$C$70/100</f>
@@ -1598,7 +1607,7 @@
     </row>
     <row r="28" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E28" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F28" s="15">
         <f>IF(F10="Sí",0,ROUND(F27*F6,2))</f>
@@ -1620,8 +1629,8 @@
     <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B6">
       <formula1>"Quincenal,Mensual,Semanal,Decenal"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B7">
-      <formula1>'Tablas oficiales'!$B$4:$B$5</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Dónde trabajas)." sqref="B7">
+      <formula1>'Sueldo neto'!$Z$1:$Z$2</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Escribe un número entre 0 y 60." sqref="B8">
       <formula1>0</formula1>
@@ -1642,7 +1651,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1651,48 +1660,57 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
+      <c r="Z1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="8">
         <v>15000</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="15">
         <f>ROUND(B5/IF(B6="Al mes",30,IF(B6="A la quincena",15,IF(B6="A la semana",7,1))),2)</f>
@@ -1700,16 +1718,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="13">
         <v>365</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F7" s="21">
         <f>IF(ISNUMBER(B8),B8,'Tablas oficiales'!$C$66)</f>
@@ -1717,14 +1735,14 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="15">
         <f>ROUND(F6*F7*MIN(B7,365)/365,2)</f>
@@ -1732,13 +1750,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="15">
         <f>INDEX('Tablas oficiales'!$C$4:$C$5,MATCH(B9,'Tablas oficiales'!$B$4:$B$5,0))</f>
@@ -1746,7 +1764,7 @@
     </row>
     <row r="10" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E10" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" s="16">
         <f>IF(F6&lt;=F9,"Sí","No")</f>
@@ -1754,12 +1772,12 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="E11" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F11" s="15">
         <f>ROUND('Tablas oficiales'!$C$76*'Tablas oficiales'!$C$68,2)</f>
@@ -1772,7 +1790,7 @@
       <c r="B12" s="24"/>
       <c r="C12" s="24"/>
       <c r="E12" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F12" s="15">
         <f>IF(F10="Sí",F8,MIN(F8,F11))</f>
@@ -1780,13 +1798,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="18">
         <f>F6</f>
       </c>
       <c r="E13" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" s="15">
         <f>ROUND(F8-F12,2)</f>
@@ -1794,7 +1812,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B14" s="25">
         <f>F7</f>
@@ -1802,24 +1820,24 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" s="18">
         <f>F8</f>
       </c>
       <c r="E15" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B16" s="18">
         <f>F12</f>
       </c>
       <c r="E16" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" s="15">
         <f>ROUND(F6*30.4,2)</f>
@@ -1827,13 +1845,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B17" s="18">
         <f>F13</f>
       </c>
       <c r="E17" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F17" s="15">
         <f>'Tablas oficiales'!$C$62*'Tablas oficiales'!$C$63/100</f>
@@ -1841,13 +1859,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="18">
         <f>F23</f>
       </c>
       <c r="E18" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F18" s="15">
         <f>F16+F13</f>
@@ -1855,13 +1873,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B19" s="20">
         <f>ROUND(F8-F23,2)</f>
       </c>
       <c r="E19" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F19" s="15">
         <f>ROUND(IF(F18&lt;=0,0,INDEX('Tablas oficiales'!$E$50:$E$60,IFERROR(MATCH(F18,'Tablas oficiales'!$B$50:$B$60,1),1))+(F18-INDEX('Tablas oficiales'!$B$50:$B$60,IFERROR(MATCH(F18,'Tablas oficiales'!$B$50:$B$60,1),1)))*INDEX('Tablas oficiales'!$D$50:$D$60,IFERROR(MATCH(F18,'Tablas oficiales'!$B$50:$B$60,1),1))/100),2)</f>
@@ -1869,7 +1887,7 @@
     </row>
     <row r="20" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E20" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F20" s="15">
         <f>ROUND(F19-IF(F18&lt;='Tablas oficiales'!$C$64,MIN(ROUND(F17,2),F19),0),2)</f>
@@ -1877,12 +1895,12 @@
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="E21" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F21" s="15">
         <f>ROUND(IF(F16&lt;=0,0,INDEX('Tablas oficiales'!$E$50:$E$60,IFERROR(MATCH(F16,'Tablas oficiales'!$B$50:$B$60,1),1))+(F16-INDEX('Tablas oficiales'!$B$50:$B$60,IFERROR(MATCH(F16,'Tablas oficiales'!$B$50:$B$60,1),1)))*INDEX('Tablas oficiales'!$D$50:$D$60,IFERROR(MATCH(F16,'Tablas oficiales'!$B$50:$B$60,1),1))/100),2)</f>
@@ -1890,7 +1908,7 @@
     </row>
     <row r="22" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E22" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F22" s="15">
         <f>ROUND(F21-IF(F16&lt;='Tablas oficiales'!$C$64,MIN(ROUND(F17,2),F21),0),2)</f>
@@ -1898,7 +1916,7 @@
     </row>
     <row r="23" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E23" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F23" s="15">
         <f>IF(F13&gt;0,ROUND(MAX(0,F20-F22),2),0)</f>
@@ -1929,8 +1947,8 @@
       <formula1>1</formula1>
       <formula2>1000000000000</formula2>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B9">
-      <formula1>'Tablas oficiales'!$B$4:$B$5</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Dónde trabajas)." sqref="B9">
+      <formula1>'Aguinaldo'!$Z$1:$Z$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1943,7 +1961,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1952,48 +1970,57 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
+      <c r="Z1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="8">
         <v>15000</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F6" s="21">
         <f>IF(AND((YEAR(B9)-YEAR(B8))&gt;0,DATE(YEAR(B8)+(YEAR(B9)-YEAR(B8)),MONTH(B8),MIN(DAY(B8),DAY(EOMONTH(DATE(YEAR(B8)+(YEAR(B9)-YEAR(B8)),MONTH(B8),1),0))))&gt;B9+1),(YEAR(B9)-YEAR(B8))-1,(YEAR(B9)-YEAR(B8)))</f>
@@ -2001,13 +2028,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F7" s="21">
         <f>B9+1-DATE(YEAR(B8)+F6,MONTH(B8),MIN(DAY(B8),DAY(EOMONTH(DATE(YEAR(B8)+F6,MONTH(B8),1),0))))</f>
@@ -2015,13 +2042,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B8" s="26">
         <v>44986</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F8" s="21">
         <f>B9-MAX(B8,DATE(YEAR(B9),1,1))+1</f>
@@ -2029,13 +2056,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B9" s="26">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F9" s="22">
         <f>F6+F7/365</f>
@@ -2043,13 +2070,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F10" s="21">
         <f>B9-B8+1</f>
@@ -2057,7 +2084,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B11" s="13">
         <v>0</v>
@@ -2065,25 +2092,25 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B12" s="27">
         <v>0</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F13" s="15">
         <f>ROUND(B6/IF(B7="Al mes",30,IF(B7="A la quincena",15,IF(B7="A la semana",7,1))),2)</f>
@@ -2091,14 +2118,14 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" s="28"/>
       <c r="C14" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F14" s="21">
         <f>IF(ISNUMBER(B13),B13,'Tablas oficiales'!$C$66)</f>
@@ -2106,7 +2133,7 @@
     </row>
     <row r="15" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E15" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F15" s="23">
         <f>IF(ISNUMBER(B14),B14,'Tablas oficiales'!$C$67)</f>
@@ -2114,12 +2141,12 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="E16" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F16" s="15">
         <f>ROUND(F13*B11,2)</f>
@@ -2132,7 +2159,7 @@
       <c r="B17" s="24"/>
       <c r="C17" s="24"/>
       <c r="E17" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F17" s="15">
         <f>ROUND(F13*F14*MIN(F8,365)/365,2)</f>
@@ -2140,16 +2167,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B18" s="29">
         <f>ROUND(F9,2)</f>
       </c>
       <c r="C18" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F18" s="21">
         <f>IF(F6+1&lt;1,0,IF(F6+1&lt;=5,'Tablas oficiales'!$C$65+2*(F6+1-1),'Tablas oficiales'!$C$65+8+2*ROUNDUP((F6+1-5)/5,0)))</f>
@@ -2157,13 +2184,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="18">
         <f>F13</f>
       </c>
       <c r="E19" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F19" s="12">
         <f>F18*F7/365</f>
@@ -2171,13 +2198,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B20" s="18">
         <f>F16</f>
       </c>
       <c r="E20" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F20" s="15">
         <f>ROUND(F13*(F19+B12),2)</f>
@@ -2185,13 +2212,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" s="18">
         <f>F17</f>
       </c>
       <c r="E21" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F21" s="15">
         <f>ROUND(F20*F15/100,2)</f>
@@ -2199,13 +2226,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B22" s="18">
         <f>F20</f>
       </c>
       <c r="E22" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F22" s="15">
         <f>INDEX('Tablas oficiales'!$C$4:$C$5,MATCH(B10,'Tablas oficiales'!$B$4:$B$5,0))</f>
@@ -2213,13 +2240,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B23" s="18">
         <f>F21</f>
       </c>
       <c r="E23" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F23" s="15">
         <f>MIN(MAX(F13,F22),'Tablas oficiales'!$C$77*F22)</f>
@@ -2227,16 +2254,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B24" s="18">
         <f>F26</f>
       </c>
       <c r="C24" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F24" s="15">
         <f>ROUND(F23*'Tablas oficiales'!$C$78*F9,2)</f>
@@ -2244,13 +2271,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B25" s="20">
         <f>ROUND(F16+F17+F20+F21+F26,2)</f>
       </c>
       <c r="E25" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F25" s="16">
         <f>IF(OR(B5="Me despidieron o terminó el contrato",F9&gt;='Tablas oficiales'!$C$79),"Sí","No")</f>
@@ -2258,7 +2285,7 @@
     </row>
     <row r="26" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E26" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F26" s="15">
         <f>IF(F25="Sí",F24,0)</f>
@@ -2266,35 +2293,35 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F29" s="15">
         <f>MAX(IF(ISNUMBER(B28),B28,F13),F13)</f>
@@ -2302,16 +2329,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B30" s="29">
         <f>ROUND(F9,2)</f>
       </c>
       <c r="C30" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="15">
         <f>ROUND(F29*'Tablas oficiales'!$C$80*30,2)</f>
@@ -2319,13 +2346,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="18">
         <f>ROUND(F29,2)</f>
       </c>
       <c r="E31" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="15">
         <f>IF(B29="Sí",ROUND(F29*'Tablas oficiales'!$C$81*F9,2),0)</f>
@@ -2333,13 +2360,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B32" s="18">
         <f>F30</f>
       </c>
       <c r="E32" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F32" s="15">
         <f>ROUND(F30+F31+F24,2)</f>
@@ -2347,13 +2374,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" s="18">
         <f>F31</f>
       </c>
       <c r="E33" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F33" s="21">
         <f>MAX(1,F6+IF(F7&gt;182,1,0))</f>
@@ -2361,13 +2388,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B34" s="18">
         <f>F24</f>
       </c>
       <c r="E34" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F34" s="15">
         <f>MIN(F32,ROUND('Tablas oficiales'!$C$82*'Tablas oficiales'!$C$68*F33,2))</f>
@@ -2375,13 +2402,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B35" s="18">
         <f>F35</f>
       </c>
       <c r="E35" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F35" s="15">
         <f>ROUND(F16+F17+F20+F21,2)</f>
@@ -2389,7 +2416,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B36" s="18">
         <f>F34</f>
@@ -2397,7 +2424,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B37" s="20">
         <f>ROUND(F32+F35,2)</f>
@@ -2405,7 +2432,7 @@
     </row>
     <row r="39" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -2421,8 +2448,8 @@
     <mergeCell ref="A39:C39"/>
   </mergeCells>
   <dataValidations count="11">
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B10">
-      <formula1>'Tablas oficiales'!$B$4:$B$5</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Dónde trabajas)." sqref="B10">
+      <formula1>'Finiquito y liquidación'!$Z$1:$Z$2</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showErrorMessage="1" error="Escribe un número entre 0 y 31." sqref="B11">
       <formula1>0</formula1>
@@ -2485,7 +2512,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -2496,7 +2523,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2507,71 +2534,71 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C4" s="33">
         <v>315.04</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="C5" s="36">
         <v>440.87</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2581,16 +2608,16 @@
       <c r="B6" s="39"/>
       <c r="C6" s="39"/>
       <c r="D6" s="39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F6" s="40" t="s">
         <v>145</v>
       </c>
       <c r="G6" s="39" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
@@ -2768,16 +2795,16 @@
       <c r="B20" s="39"/>
       <c r="C20" s="39"/>
       <c r="D20" s="39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F20" s="40" t="s">
         <v>145</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
@@ -2955,16 +2982,16 @@
       <c r="B34" s="39"/>
       <c r="C34" s="39"/>
       <c r="D34" s="39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E34" s="39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F34" s="40" t="s">
         <v>145</v>
       </c>
       <c r="G34" s="39" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
@@ -3142,16 +3169,16 @@
       <c r="B48" s="39"/>
       <c r="C48" s="39"/>
       <c r="D48" s="39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E48" s="39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F48" s="40" t="s">
         <v>145</v>
       </c>
       <c r="G48" s="39" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
@@ -3333,7 +3360,7 @@
         <v>3566.22</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E62" s="32" t="s">
         <v>155</v>
@@ -3342,7 +3369,7 @@
         <v>156</v>
       </c>
       <c r="G62" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3365,7 +3392,7 @@
         <v>159</v>
       </c>
       <c r="G63" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3379,16 +3406,16 @@
         <v>11492.66</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E64" s="32" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F64" s="34" t="s">
         <v>159</v>
       </c>
       <c r="G64" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3411,7 +3438,7 @@
         <v>164</v>
       </c>
       <c r="G65" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3434,7 +3461,7 @@
         <v>164</v>
       </c>
       <c r="G66" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3457,7 +3484,7 @@
         <v>164</v>
       </c>
       <c r="G67" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3471,7 +3498,7 @@
         <v>117.31</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E68" s="32" t="s">
         <v>155</v>
@@ -3480,7 +3507,7 @@
         <v>156</v>
       </c>
       <c r="G68" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3503,7 +3530,7 @@
         <v>172</v>
       </c>
       <c r="G69" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3526,7 +3553,7 @@
         <v>172</v>
       </c>
       <c r="G70" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3549,7 +3576,7 @@
         <v>172</v>
       </c>
       <c r="G71" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3572,7 +3599,7 @@
         <v>172</v>
       </c>
       <c r="G72" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3595,7 +3622,7 @@
         <v>172</v>
       </c>
       <c r="G73" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3618,7 +3645,7 @@
         <v>172</v>
       </c>
       <c r="G74" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3641,7 +3668,7 @@
         <v>172</v>
       </c>
       <c r="G75" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -3664,7 +3691,7 @@
         <v>182</v>
       </c>
       <c r="G76" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3687,7 +3714,7 @@
         <v>164</v>
       </c>
       <c r="G77" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3710,7 +3737,7 @@
         <v>164</v>
       </c>
       <c r="G78" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3733,7 +3760,7 @@
         <v>164</v>
       </c>
       <c r="G79" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3756,7 +3783,7 @@
         <v>164</v>
       </c>
       <c r="G80" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3779,7 +3806,7 @@
         <v>164</v>
       </c>
       <c r="G81" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -3802,7 +3829,7 @@
         <v>182</v>
       </c>
       <c r="G82" s="32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito y liquidación»: pones tus fechas y tu sueldo, y te dice el finiquito (salarios, aguinaldo, vacaciones y primas) y, si te despidieron sin causa justificada, la liquidación.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -410,7 +410,7 @@
     <t>Tablas oficiales de México</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2059,7 +2059,7 @@
         <v>88</v>
       </c>
       <c r="B9" s="26">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>89</v>

--- a/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/mx/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Finiquito y liquidación»: pones tus fechas y tu sueldo, y te dice el finiquito (salarios, aguinaldo, vacaciones y primas) y, si te despidieron sin causa justificada, la liquidación.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 22/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga te baja la versión nueva.</t>
@@ -410,7 +410,7 @@
     <t>Tablas oficiales de México</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 22/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -2059,7 +2059,7 @@
         <v>88</v>
       </c>
       <c r="B9" s="26">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>89</v>
